--- a/Finalisation-concertation/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/Finalisation-concertation/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:36:59+00:00</t>
+    <t>2026-05-21T12:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Finalisation-concertation/ig/StructureDefinition-fr-medicationrequest.xlsx
+++ b/Finalisation-concertation/ig/StructureDefinition-fr-medicationrequest.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-medicationrequest</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-medicationrequest</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:38:31+00:00</t>
+    <t>2026-05-21T13:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -486,7 +486,7 @@
     <t>treatmentIntent</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-treatment-intent}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-treatment-intent}
 </t>
   </si>
   <si>
@@ -545,7 +545,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-treatment-intent</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-treatment-intent</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -576,7 +576,7 @@
     <t>SNOMED CT encoded treatment overall intent</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/ValueSet/fr-treatment-intent</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/ValueSet/fr-treatment-intent</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -946,7 +946,7 @@
     <t>medicationReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-medication-noncompound|https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-medication-compound)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-medication-noncompound|https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-medication-compound)
 </t>
   </si>
   <si>
@@ -956,7 +956,7 @@
     <t>medicationCodeableConcept</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/ValueSet/fr-medication-code</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/ValueSet/fr-medication-code</t>
   </si>
   <si>
     <t>MedicationRequest.subject</t>
@@ -1550,7 +1550,7 @@
     <t>AdditionalWhenValues</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-additional-when-values}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-additional-when-values}
 </t>
   </si>
   <si>
@@ -1911,7 +1911,7 @@
     <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/ValueSet/fr-route-of-administration</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/ValueSet/fr-route-of-administration</t>
   </si>
   <si>
     <t>Dosage.route</t>
@@ -1938,7 +1938,7 @@
     <t>A coded value indicating the method by which the medication is introduced into or onto the body. Most commonly used for injections.  For examples, Slow Push; Deep IV.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/ValueSet/FrMethodOfAdministration</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/ValueSet/FrMethodOfAdministration</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -1977,7 +1977,7 @@
     <t>BasisOfDoseComponent</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-basis-of-dose-component}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-basis-of-dose-component}
 </t>
   </si>
   <si>
@@ -2042,7 +2042,7 @@
     <t>doseRange</t>
   </si>
   <si>
-    <t xml:space="preserve">Range {https://hl7.fr/ig/fhir/medication/StructureDefinition/FrRangeMedication}
+    <t xml:space="preserve">Range {https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/FrRangeMedication}
 </t>
   </si>
   <si>
@@ -2052,7 +2052,7 @@
     <t>doseQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {https://hl7.fr/ig/fhir/medication/StructureDefinition/FrSimpleQuantityMedication}
+    <t xml:space="preserve">Quantity {https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/FrSimpleQuantityMedication}
 </t>
   </si>
   <si>
@@ -2092,7 +2092,7 @@
     <t>rateRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {https://hl7.fr/ig/fhir/medication/StructureDefinition/FrRatioMedication}
+    <t xml:space="preserve">Ratio {https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/FrRatioMedication}
 </t>
   </si>
   <si>
@@ -2850,7 +2850,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="132.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="140.80078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
